--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/post DFS_HRM-2031-0360/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.46472</v>
+        <v>17.00468</v>
       </c>
       <c r="D2" t="n">
-        <v>16.9211</v>
+        <v>16.67611</v>
       </c>
       <c r="E2" t="n">
-        <v>16.84589</v>
+        <v>16.94905</v>
       </c>
       <c r="F2" t="n">
-        <v>42.95728</v>
+        <v>42.33997</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05156</v>
+        <v>0.05031</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82566</v>
+        <v>1.83033</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.04006</v>
+        <v>16.97176</v>
       </c>
       <c r="D3" t="n">
-        <v>16.48128</v>
+        <v>16.54407</v>
       </c>
       <c r="E3" t="n">
-        <v>16.55154</v>
+        <v>16.78388</v>
       </c>
       <c r="F3" t="n">
-        <v>42.91947</v>
+        <v>42.9209</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05092</v>
+        <v>0.05063</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83079</v>
+        <v>1.82293</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.7765</v>
+        <v>16.72265</v>
       </c>
       <c r="D4" t="n">
-        <v>16.61297</v>
+        <v>16.60536</v>
       </c>
       <c r="E4" t="n">
-        <v>16.79452</v>
+        <v>16.61019</v>
       </c>
       <c r="F4" t="n">
-        <v>42.87288</v>
+        <v>42.79426</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05056</v>
+        <v>0.05064</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87577</v>
+        <v>1.81655</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.38219</v>
+        <v>16.76044</v>
       </c>
       <c r="D6" t="n">
-        <v>16.32375</v>
+        <v>15.79274</v>
       </c>
       <c r="E6" t="n">
-        <v>16.2241</v>
+        <v>16.28929</v>
       </c>
       <c r="F6" t="n">
-        <v>21.82162</v>
+        <v>21.80446</v>
       </c>
       <c r="G6" t="n">
-        <v>34.12316</v>
+        <v>34.34142</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.8746</v>
+        <v>16.97961</v>
       </c>
       <c r="D7" t="n">
-        <v>16.03384</v>
+        <v>16.00861</v>
       </c>
       <c r="E7" t="n">
-        <v>16.43104</v>
+        <v>16.33204</v>
       </c>
       <c r="F7" t="n">
-        <v>21.28366</v>
+        <v>21.81067</v>
       </c>
       <c r="G7" t="n">
-        <v>33.9271</v>
+        <v>33.9792</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.68935</v>
+        <v>16.99478</v>
       </c>
       <c r="D8" t="n">
-        <v>16.10881</v>
+        <v>15.99665</v>
       </c>
       <c r="E8" t="n">
-        <v>16.1795</v>
+        <v>16.58769</v>
       </c>
       <c r="F8" t="n">
-        <v>22.04557</v>
+        <v>21.9874</v>
       </c>
       <c r="G8" t="n">
-        <v>33.64558</v>
+        <v>33.69667</v>
       </c>
     </row>
   </sheetData>
